--- a/saitama-kobun4/gas/古典クエスト_問題マスター.xlsx
+++ b/saitama-kobun4/gas/古典クエスト_問題マスター.xlsx
@@ -77,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -90,6 +90,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -456,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A68"/>
+  <dimension ref="A1:A77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -899,6 +902,65 @@
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  ※ 口語訳のルビ（class="gl"）と入れ子にはできません。どちらか一方にしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>【用途】</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>本文シートの「用途」列で、その大問をどちらで出すかを決めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  練習    … ふだんの練習に出る（空欄もこの扱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  小テスト … 授業の小テストにだけ出る。練習の一覧には出ないので、</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            生徒は事前に読むことができません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>小テストは、その生徒がまだ出されていない大問からランダムに選ばれます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>一度出た大問は、その生徒には二度と出ません。残りが足りなくなったら、</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>この列が「小テスト」の行を増やしてください。</t>
         </is>
       </c>
     </row>
@@ -913,7 +975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -924,7 +986,7 @@
     <col width="70" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
     <col width="66" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -971,10 +1033,15 @@
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
           <t>表示順</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>公開</t>
         </is>
@@ -1021,10 +1088,15 @@
           <t>&lt;p&gt;これも今となっては昔のことだが、絵仏師の良秀という者がいた。隣の家から火が出て、風が吹きつけて火が迫ってきたので、逃げ出して大通りへ出てしまった。家の中には、人が注文して描かせている仏の絵もあった。また、着物も着ていない妻子などもそのまま家の中にいた。良秀はそれも気にかけず、ただ自分が逃げ出したことだけをよいことにして、向かい側に立っていた。&lt;/p&gt;&lt;p&gt;見ると、すでに火は自分の家に燃え移って、煙や炎がくすぶり出すまで、ずっと向かい側に立って眺めていたので、「驚きあきれたことだ」と言って、人々が見舞いに来たけれども、（良秀は）騒がない。「どうしたのか」と人が言うと、向かい側に立って、自分の家が焼けるのを見て、うなずいて、時々笑った。「ああ、たいそうなもうけものをしたことだ。長年、まずく描いていたものだなあ」と言うので、見舞いに来ていた者たちが、「これはどうしたことか、こうして立っていらっしゃるのか。物の怪でも取りつきなさったのか」と言うと、「どうして物の怪が取りつくものか。長年、不動明王の火炎をうまく描けずにいたのだ。今見ると、このように燃えるのだったのだなと、会得したのだ。これこそもうけものだ」と言って、あざ笑って立っていた。&lt;/p&gt;&lt;p&gt;その後のことであろうか、良秀のよじり不動といって、今でも人々がほめ合っている。&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>練習</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1071,10 +1143,15 @@
           <t>&lt;p&gt;和泉式部が、（夫の）保昌の妻として丹後の国に下っていたころ、京で歌合があったが、（娘の）小式部内侍が歌のよみ手に選ばれて歌をよんだところ、定頼中納言がふざけて、小式部内侍がいたところに来て、「丹後へおやりになった使いは帰って参りましたか。（返事が来ないので）どんなに待ち遠しくお思いでしょう」と言って、部屋の前を通り過ぎられたのを、（小式部内侍は）御簾から身を半分ほど乗り出して、わずかに（定頼の）直衣の袖を引きとめて、&lt;/p&gt;&lt;p&gt;「大江山を越え、生野を通って行く道が遠いので、まだ天の橋立の地を踏んでもいませんし、母からの手紙も見ていません」&lt;/p&gt;&lt;p&gt;とよみかけた。（定頼は）思いがけないことに驚きあきれて、「これはどうしたことだ、こんなことがあってよいものか」とだけ言って、返歌をすることもできず、袖を引き放ってお逃げになった。小式部内侍は、これ以降、歌よみとしての評判が世に立つようになった。&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>小テスト</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1121,10 +1198,15 @@
           <t>&lt;p&gt;木登りの名人といわれた男が、人に指図して高い木に登らせて枝の先を切らせたときに、たいそう危なく見えたうちは何も言わないで、（その人が）降りるときに、軒の高さくらいになって、「けがをするな。気をつけて降りろ」と声をかけましたので、「これくらいの高さになれば、飛び降りても降りられるでしょう。どうしてそのように言うのか」と申しましたところ、「そのことでございます。目がくらむほど高く、枝が危ないうちは、本人が自分で恐れておりますので、（私は）何も申しません。けがは、安全な所になってから、必ずするものでございます」と言う。&lt;/p&gt;&lt;p&gt;身分の低い者であるけれども、その言葉は聖人の戒めと一致している。蹴鞠でも、難しい所を蹴り出したあと、（もう）簡単だと思うと、必ず落とすと申すようです。&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>練習</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1171,10 +1253,15 @@
           <t>&lt;p&gt;仁和寺にいるある法師が、年をとるまで石清水八幡宮を参拝したことがなかったので、物足りなく思って、あるとき思い立って、ただ一人、徒歩で参拝した。（ふもとの）極楽寺や高良神社などを拝んで、これだけのものだと思い込んで帰ってしまった。&lt;/p&gt;&lt;p&gt;さて、仲間に会って、「長年思っていたことを、果たしました。聞いていた以上に尊くていらっしゃった。それにしても、参拝する人がみな山へ登っていたのは、何事があったのだろうか、知りたかったけれど、神にお参りすることこそが本来の目的だと思って、山の上までは見ませんでした」と言った。&lt;/p&gt;&lt;p&gt;ちょっとしたことにも、案内者はいてほしいものである。&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>小テスト</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1221,10 +1308,15 @@
           <t>&lt;p&gt;これも今となっては昔のことだが、比叡山に児がいた。僧たちが、宵の手持ちぶさたなときに、「さあ、ぼたもちを作ろう」と言ったのを、この児は期待して聞いた。とはいっても、作り上げるのを待って寝ないでいるのもみっともないだろうと思って、部屋の片隅に寄って、寝たふりをして、出てくるのを待っていたところ、もう作り上げた様子で、大騒ぎしている。&lt;/p&gt;&lt;p&gt;この児は、きっと（僧たちが）起こしてくれるだろうと待っていたところ、僧が「もしもし。お目をお覚ましください」と言うのを、うれしいとは思うけれども、たった一度で返事をするのも、待っていたのかと思われては困ると思って、もう一声呼ばれてから返事をしようと、我慢して寝ているうちに、「これ、お起こし申し上げるな。幼い人は寝入っておしまいになった」と言う声がしたので、ああ、がっかりだと思って、もう一度起こしてくれよと思いながら寝て聞いていると、むしゃむしゃとひたすら食べる音がしたので、どうしようもなくて、ずいぶん時間がたってから、「はい」と返事をしたので、僧たちは笑うことこのうえなかった。&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>練習</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1271,10 +1363,15 @@
           <t>&lt;p&gt;ある川のほとりで、蟻が遊んでいることがあった。急に水かさが増して、その蟻を（水が）さらって流す。浮いたり沈んだりしているところに、鳩が枝の先からこれを見て、「かわいそうなありさまだなあ」と（思い）、枝を少し食い切って川の中へ落としたところ、蟻はこれに乗って、水ぎわに上がった。&lt;/p&gt;&lt;p&gt;そうしているところに、ある人が、竿の先に鳥もちを付けて、その鳩を捕らえようとする。蟻が心に思うことには、「たった今受けた恩を返そう」と思い、その人の足にしっかりとかみついたので、（その人は）驚いて、竿をあちらへ投げ捨ててしまった。鳩はこれに気づいて、はるかな空へと逃げのびた。&lt;/p&gt;&lt;p&gt;そのように、人の恩を受けたような者は、どのようにしてでもその恩に報いるべきである。&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>練習</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1321,10 +1418,15 @@
           <t>&lt;p&gt;今となっては昔のことだが、小野篁という人がいらっしゃった。嵯峨天皇の御代に、内裏に札が立ててあったが、（そこには）「無悪善」と書いてあった。帝が篁に「読め」とおっしゃったので、（篁は）「読むことは読めるでしょう。しかし、恐れ多いことでございますので、申し上げることはできません」と申し上げたところ、「かまわないから申せ」と、たびたびおっしゃったので、「『さが（＝嵯峨天皇）なくてよからん』と書いてございます。つまり、帝を呪い申し上げているのでございます」と申し上げたところ、（帝は）「おまえのほかに、誰がこんなものを書くだろうか」とおっしゃったので、「だからこそ、申し上げますまいと申したのでございます」と申し上げると、帝は「それでは、どんなものが書いてあっても読めるのか」とおっしゃったので、「何であっても読めましょう」と申したので、片仮名の「子」という文字を十二お書かせになって、「読め」とおっしゃったところ、「ねこの子のこねこ、ししの子のこじし」と読んだので、帝はほほえみなさって、何事もなく終わった。&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>小テスト</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1371,10 +1473,15 @@
           <t>&lt;p&gt;ある人が弓を射ることを習うときに、二本の矢を手にはさんで的に向かった。師が言うことには、「初心者は二本の矢を持ってはならない。あとの矢をあてにして、初めの矢をいいかげんに射る心が生じる。毎回、ただ当たり外れを考えず、この一本の矢で決めようと思え」と言う。わずか二本の矢を、師の前で一本をいいかげんにしようと思うだろうか（いや、思わない）。しかし、なまけ心は、自分では気づかないけれども、師はこれを見抜いている。この戒めは、すべてのことにあてはまるはずだ。&lt;/p&gt;&lt;p&gt;仏道を学ぶ人は、夜には翌朝があると思い、朝には夕方があると思って、あらためて念入りに修行しようとあてにする。まして、ほんの一瞬のうちに、なまけ心があることに気づくだろうか（いや、気づかない）。どうして、ただ今のこの一瞬において、すぐに実行することが、こんなにも難しいのか。&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>練習</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1421,10 +1528,15 @@
           <t>&lt;p&gt;ある山寺で、四人の僧が集まって、七日の間、無言の行を始めた。ある夜、風が吹いて、仏前のあかりが消えてしまったので、いちばん下位の僧が、こらえきれずに「火が消えた。早くともせ」と言う。&lt;/p&gt;&lt;p&gt;二番目の僧が、これを聞いて、「無言の行なのに、ものを言ってよいものか」と、不愉快そうに非難した。三番目の僧は、「二人ともものを言ってしまった。情けないことだ」と言う。&lt;/p&gt;&lt;p&gt;いちばん上位の僧は、うなずいて、「私一人だけは、ものを言っていない」と言った。&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>小テスト</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1471,10 +1583,15 @@
           <t>&lt;p&gt;陰暦九月二十日ごろ、ある人にお誘いいただいて、夜明けまで月を見て歩き回ることがありましたが、（その人が）思い出しなさる家があって、取り次ぎを頼んでお入りになった。荒れた庭に露がたくさん降りているところに、わざとらしくない自然な香のかおりがしっとりと漂って、ひっそりと暮らしている様子が、たいそうしみじみと趣深い。&lt;/p&gt;&lt;p&gt;ちょうどよい頃合いで（その人は）お出になったけれど、やはりその場のようすが優雅に思われて、物陰からしばらく見ていたところ、（家の女主人は）両開きの戸をもう少し押し開けて、月を見ている様子である。もし（客を送り出して）すぐに戸を閉めて引きこもってしまったなら、残念であっただろう。（客が帰った）あとまで見ている人がいようとは、どうして知っていようか。このようなことは、ただ、ふだんからの心がけによるものであろう。&lt;/p&gt;&lt;p&gt;その人は、まもなく亡くなってしまったと聞きました。&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>小テスト</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
